--- a/artfynd/A 33964-2023 artfynd.xlsx
+++ b/artfynd/A 33964-2023 artfynd.xlsx
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125412210</v>
+        <v>125409301</v>
       </c>
       <c r="B6" t="n">
-        <v>78810</v>
+        <v>79919</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,25 +1095,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>582813</v>
+        <v>582972</v>
       </c>
       <c r="R6" t="n">
-        <v>7079908</v>
+        <v>7079774</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125409301</v>
+        <v>125412210</v>
       </c>
       <c r="B7" t="n">
-        <v>79919</v>
+        <v>78810</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1197,25 +1197,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>582972</v>
+        <v>582813</v>
       </c>
       <c r="R7" t="n">
-        <v>7079774</v>
+        <v>7079908</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>

--- a/artfynd/A 33964-2023 artfynd.xlsx
+++ b/artfynd/A 33964-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125412906</v>
+        <v>125408929</v>
       </c>
       <c r="B2" t="n">
-        <v>78810</v>
+        <v>91030</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>582971</v>
+        <v>582879</v>
       </c>
       <c r="R2" t="n">
-        <v>7079630</v>
+        <v>7079836</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125408990</v>
+        <v>125412399</v>
       </c>
       <c r="B3" t="n">
-        <v>91012</v>
+        <v>79920</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>6462</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>582898</v>
+        <v>582861</v>
       </c>
       <c r="R3" t="n">
-        <v>7079836</v>
+        <v>7079872</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125409242</v>
+        <v>125409301</v>
       </c>
       <c r="B5" t="n">
-        <v>78810</v>
+        <v>79919</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +993,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>582988</v>
+        <v>582972</v>
       </c>
       <c r="R5" t="n">
-        <v>7079828</v>
+        <v>7079774</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125409301</v>
+        <v>125412570</v>
       </c>
       <c r="B6" t="n">
-        <v>79919</v>
+        <v>57529</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,38 +1095,43 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6461</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Omsjöflärken, Omsjöflärken, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>582972</v>
+        <v>582867</v>
       </c>
       <c r="R6" t="n">
-        <v>7079774</v>
+        <v>7079848</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1185,10 +1190,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125412210</v>
+        <v>125410122</v>
       </c>
       <c r="B7" t="n">
-        <v>78810</v>
+        <v>92293</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1197,25 +1202,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1230,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>582813</v>
+        <v>583046</v>
       </c>
       <c r="R7" t="n">
-        <v>7079908</v>
+        <v>7079760</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1287,10 +1292,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125410433</v>
+        <v>125408990</v>
       </c>
       <c r="B8" t="n">
-        <v>79891</v>
+        <v>91012</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1303,21 +1308,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1332,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>583110</v>
+        <v>582898</v>
       </c>
       <c r="R8" t="n">
-        <v>7079768</v>
+        <v>7079836</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1389,7 +1394,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125409899</v>
+        <v>125408385</v>
       </c>
       <c r="B9" t="n">
         <v>78810</v>
@@ -1429,10 +1434,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>583044</v>
+        <v>582906</v>
       </c>
       <c r="R9" t="n">
-        <v>7079761</v>
+        <v>7079758</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1491,10 +1496,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125410256</v>
+        <v>125410318</v>
       </c>
       <c r="B10" t="n">
-        <v>92293</v>
+        <v>92490</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1503,25 +1508,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4364</v>
+        <v>2079</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1531,7 +1536,7 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>583089</v>
+        <v>583090</v>
       </c>
       <c r="R10" t="n">
         <v>7079781</v>
@@ -1593,10 +1598,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125412777</v>
+        <v>125409866</v>
       </c>
       <c r="B11" t="n">
-        <v>78810</v>
+        <v>82597</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1609,21 +1614,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1633,10 +1638,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>582936</v>
+        <v>583043</v>
       </c>
       <c r="R11" t="n">
-        <v>7079714</v>
+        <v>7079761</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1695,10 +1700,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125410122</v>
+        <v>125409899</v>
       </c>
       <c r="B12" t="n">
-        <v>92293</v>
+        <v>78810</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1707,25 +1712,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1735,10 +1740,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>583046</v>
+        <v>583044</v>
       </c>
       <c r="R12" t="n">
-        <v>7079760</v>
+        <v>7079761</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1797,10 +1802,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125412324</v>
+        <v>125410433</v>
       </c>
       <c r="B13" t="n">
-        <v>79919</v>
+        <v>79891</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1809,25 +1814,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6461</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1837,10 +1842,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>582860</v>
+        <v>583110</v>
       </c>
       <c r="R13" t="n">
-        <v>7079878</v>
+        <v>7079768</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1899,10 +1904,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125412472</v>
+        <v>125412381</v>
       </c>
       <c r="B14" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1915,21 +1920,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1939,10 +1944,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>582841</v>
+        <v>582862</v>
       </c>
       <c r="R14" t="n">
-        <v>7079874</v>
+        <v>7079873</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2001,10 +2006,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125412758</v>
+        <v>125409344</v>
       </c>
       <c r="B15" t="n">
-        <v>79891</v>
+        <v>74901</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2017,21 +2022,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2041,10 +2046,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>582922</v>
+        <v>582972</v>
       </c>
       <c r="R15" t="n">
-        <v>7079716</v>
+        <v>7079774</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2103,10 +2108,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125410683</v>
+        <v>125412906</v>
       </c>
       <c r="B16" t="n">
-        <v>78455</v>
+        <v>78810</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2119,21 +2124,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2143,10 +2148,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>583125</v>
+        <v>582971</v>
       </c>
       <c r="R16" t="n">
-        <v>7079741</v>
+        <v>7079630</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2205,10 +2210,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125410318</v>
+        <v>125412758</v>
       </c>
       <c r="B17" t="n">
-        <v>92490</v>
+        <v>79891</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2221,21 +2226,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2079</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2245,10 +2250,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>583090</v>
+        <v>582922</v>
       </c>
       <c r="R17" t="n">
-        <v>7079781</v>
+        <v>7079716</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2307,10 +2312,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125412823</v>
+        <v>125410256</v>
       </c>
       <c r="B18" t="n">
-        <v>78810</v>
+        <v>92293</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2319,25 +2324,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2347,10 +2352,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>582969</v>
+        <v>583089</v>
       </c>
       <c r="R18" t="n">
-        <v>7079681</v>
+        <v>7079781</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2409,10 +2414,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125409866</v>
+        <v>125412777</v>
       </c>
       <c r="B19" t="n">
-        <v>82597</v>
+        <v>78810</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2425,21 +2430,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2449,10 +2454,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>583043</v>
+        <v>582936</v>
       </c>
       <c r="R19" t="n">
-        <v>7079761</v>
+        <v>7079714</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2511,10 +2516,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125410480</v>
+        <v>125412472</v>
       </c>
       <c r="B20" t="n">
-        <v>78547</v>
+        <v>78810</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2527,21 +2532,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2551,10 +2556,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>583113</v>
+        <v>582841</v>
       </c>
       <c r="R20" t="n">
-        <v>7079748</v>
+        <v>7079874</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2613,10 +2618,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125409828</v>
+        <v>125412324</v>
       </c>
       <c r="B21" t="n">
-        <v>79891</v>
+        <v>79919</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2625,25 +2630,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>6461</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2653,10 +2658,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>583020</v>
+        <v>582860</v>
       </c>
       <c r="R21" t="n">
-        <v>7079742</v>
+        <v>7079878</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2715,10 +2720,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125412381</v>
+        <v>125411016</v>
       </c>
       <c r="B22" t="n">
-        <v>79891</v>
+        <v>78546</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2731,21 +2736,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2755,10 +2760,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>582862</v>
+        <v>583096</v>
       </c>
       <c r="R22" t="n">
-        <v>7079873</v>
+        <v>7079716</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2817,10 +2822,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125412291</v>
+        <v>125410683</v>
       </c>
       <c r="B23" t="n">
-        <v>79891</v>
+        <v>78455</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2833,21 +2838,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>353</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2857,10 +2862,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>582860</v>
+        <v>583125</v>
       </c>
       <c r="R23" t="n">
-        <v>7079878</v>
+        <v>7079741</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -2919,10 +2924,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125408929</v>
+        <v>125412210</v>
       </c>
       <c r="B24" t="n">
-        <v>91030</v>
+        <v>78810</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2935,21 +2940,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2959,10 +2964,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>582879</v>
+        <v>582813</v>
       </c>
       <c r="R24" t="n">
-        <v>7079836</v>
+        <v>7079908</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3021,10 +3026,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125412399</v>
+        <v>125412823</v>
       </c>
       <c r="B25" t="n">
-        <v>79920</v>
+        <v>78810</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3033,25 +3038,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3061,10 +3066,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>582861</v>
+        <v>582969</v>
       </c>
       <c r="R25" t="n">
-        <v>7079872</v>
+        <v>7079681</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3123,10 +3128,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125411016</v>
+        <v>125409828</v>
       </c>
       <c r="B26" t="n">
-        <v>78546</v>
+        <v>79891</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3139,21 +3144,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3163,10 +3168,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>583096</v>
+        <v>583020</v>
       </c>
       <c r="R26" t="n">
-        <v>7079716</v>
+        <v>7079742</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3225,10 +3230,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125408385</v>
+        <v>125410480</v>
       </c>
       <c r="B27" t="n">
-        <v>78810</v>
+        <v>78547</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3241,21 +3246,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3265,10 +3270,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>582906</v>
+        <v>583113</v>
       </c>
       <c r="R27" t="n">
-        <v>7079758</v>
+        <v>7079748</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3327,10 +3332,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125409344</v>
+        <v>125412291</v>
       </c>
       <c r="B28" t="n">
-        <v>74901</v>
+        <v>79891</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3343,21 +3348,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6440</v>
+        <v>6458</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3367,10 +3372,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>582972</v>
+        <v>582860</v>
       </c>
       <c r="R28" t="n">
-        <v>7079774</v>
+        <v>7079878</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3531,10 +3536,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125412570</v>
+        <v>125409242</v>
       </c>
       <c r="B30" t="n">
-        <v>57529</v>
+        <v>78810</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3547,39 +3552,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Omsjöflärken, Omsjöflärken, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>582867</v>
+        <v>582988</v>
       </c>
       <c r="R30" t="n">
-        <v>7079848</v>
+        <v>7079828</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>

--- a/artfynd/A 33964-2023 artfynd.xlsx
+++ b/artfynd/A 33964-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125408929</v>
+        <v>125410122</v>
       </c>
       <c r="B2" t="n">
-        <v>91030</v>
+        <v>92448</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>582879</v>
+        <v>583046</v>
       </c>
       <c r="R2" t="n">
-        <v>7079836</v>
+        <v>7079760</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125412399</v>
+        <v>125409866</v>
       </c>
       <c r="B3" t="n">
-        <v>79920</v>
+        <v>82737</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6462</v>
+        <v>1312</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>582861</v>
+        <v>583043</v>
       </c>
       <c r="R3" t="n">
-        <v>7079872</v>
+        <v>7079761</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125408754</v>
+        <v>125412906</v>
       </c>
       <c r="B4" t="n">
-        <v>78810</v>
+        <v>78947</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>582870</v>
+        <v>582971</v>
       </c>
       <c r="R4" t="n">
-        <v>7079809</v>
+        <v>7079630</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125409301</v>
+        <v>125411016</v>
       </c>
       <c r="B5" t="n">
-        <v>79919</v>
+        <v>78683</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +993,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6461</v>
+        <v>6446</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>582972</v>
+        <v>583096</v>
       </c>
       <c r="R5" t="n">
-        <v>7079774</v>
+        <v>7079716</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125412570</v>
+        <v>125408990</v>
       </c>
       <c r="B6" t="n">
-        <v>57529</v>
+        <v>91166</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,39 +1099,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Omsjöflärken, Omsjöflärken, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>582867</v>
+        <v>582898</v>
       </c>
       <c r="R6" t="n">
-        <v>7079848</v>
+        <v>7079836</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1190,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125410122</v>
+        <v>125412399</v>
       </c>
       <c r="B7" t="n">
-        <v>92293</v>
+        <v>80057</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1206,21 +1201,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4364</v>
+        <v>6462</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1230,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>583046</v>
+        <v>582861</v>
       </c>
       <c r="R7" t="n">
-        <v>7079760</v>
+        <v>7079872</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1292,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125408990</v>
+        <v>125412291</v>
       </c>
       <c r="B8" t="n">
-        <v>91012</v>
+        <v>80028</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1308,21 +1303,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1332,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>582898</v>
+        <v>582860</v>
       </c>
       <c r="R8" t="n">
-        <v>7079836</v>
+        <v>7079878</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1394,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125408385</v>
+        <v>125409344</v>
       </c>
       <c r="B9" t="n">
-        <v>78810</v>
+        <v>75025</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1410,21 +1405,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1434,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>582906</v>
+        <v>582972</v>
       </c>
       <c r="R9" t="n">
-        <v>7079758</v>
+        <v>7079774</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1496,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125410318</v>
+        <v>125412210</v>
       </c>
       <c r="B10" t="n">
-        <v>92490</v>
+        <v>78947</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1512,21 +1507,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2079</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1536,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>583090</v>
+        <v>582813</v>
       </c>
       <c r="R10" t="n">
-        <v>7079781</v>
+        <v>7079908</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1598,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125409866</v>
+        <v>125409301</v>
       </c>
       <c r="B11" t="n">
-        <v>82597</v>
+        <v>80056</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1610,25 +1605,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1312</v>
+        <v>6461</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1638,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>583043</v>
+        <v>582972</v>
       </c>
       <c r="R11" t="n">
-        <v>7079761</v>
+        <v>7079774</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1700,10 +1695,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125409899</v>
+        <v>125408929</v>
       </c>
       <c r="B12" t="n">
-        <v>78810</v>
+        <v>91184</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1716,21 +1711,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1740,10 +1735,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>583044</v>
+        <v>582879</v>
       </c>
       <c r="R12" t="n">
-        <v>7079761</v>
+        <v>7079836</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1802,10 +1797,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125410433</v>
+        <v>125409828</v>
       </c>
       <c r="B13" t="n">
-        <v>79891</v>
+        <v>80028</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1842,10 +1837,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>583110</v>
+        <v>583020</v>
       </c>
       <c r="R13" t="n">
-        <v>7079768</v>
+        <v>7079742</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1904,10 +1899,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125412381</v>
+        <v>125410256</v>
       </c>
       <c r="B14" t="n">
-        <v>79891</v>
+        <v>92448</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1916,25 +1911,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1944,10 +1939,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>582862</v>
+        <v>583089</v>
       </c>
       <c r="R14" t="n">
-        <v>7079873</v>
+        <v>7079781</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2006,10 +2001,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125409344</v>
+        <v>125410683</v>
       </c>
       <c r="B15" t="n">
-        <v>74901</v>
+        <v>78592</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2022,21 +2017,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6440</v>
+        <v>353</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2046,10 +2041,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>582972</v>
+        <v>583125</v>
       </c>
       <c r="R15" t="n">
-        <v>7079774</v>
+        <v>7079741</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2108,10 +2103,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125412906</v>
+        <v>125410480</v>
       </c>
       <c r="B16" t="n">
-        <v>78810</v>
+        <v>78684</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2124,21 +2119,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2148,10 +2143,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>582971</v>
+        <v>583113</v>
       </c>
       <c r="R16" t="n">
-        <v>7079630</v>
+        <v>7079748</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2210,10 +2205,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125412758</v>
+        <v>125409899</v>
       </c>
       <c r="B17" t="n">
-        <v>79891</v>
+        <v>78947</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2226,21 +2221,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2250,10 +2245,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>582922</v>
+        <v>583044</v>
       </c>
       <c r="R17" t="n">
-        <v>7079716</v>
+        <v>7079761</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2312,10 +2307,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125410256</v>
+        <v>125410433</v>
       </c>
       <c r="B18" t="n">
-        <v>92293</v>
+        <v>80028</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2324,25 +2319,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2352,10 +2347,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>583089</v>
+        <v>583110</v>
       </c>
       <c r="R18" t="n">
-        <v>7079781</v>
+        <v>7079768</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2417,7 +2412,7 @@
         <v>125412777</v>
       </c>
       <c r="B19" t="n">
-        <v>78810</v>
+        <v>78947</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2516,10 +2511,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125412472</v>
+        <v>125412758</v>
       </c>
       <c r="B20" t="n">
-        <v>78810</v>
+        <v>80028</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2532,21 +2527,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2556,10 +2551,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>582841</v>
+        <v>582922</v>
       </c>
       <c r="R20" t="n">
-        <v>7079874</v>
+        <v>7079716</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2618,10 +2613,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125412324</v>
+        <v>125412472</v>
       </c>
       <c r="B21" t="n">
-        <v>79919</v>
+        <v>78947</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2630,25 +2625,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2658,10 +2653,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>582860</v>
+        <v>582841</v>
       </c>
       <c r="R21" t="n">
-        <v>7079878</v>
+        <v>7079874</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2720,10 +2715,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125411016</v>
+        <v>125408385</v>
       </c>
       <c r="B22" t="n">
-        <v>78546</v>
+        <v>78947</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2736,21 +2731,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2760,10 +2755,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>583096</v>
+        <v>582906</v>
       </c>
       <c r="R22" t="n">
-        <v>7079716</v>
+        <v>7079758</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2822,10 +2817,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125410683</v>
+        <v>125410376</v>
       </c>
       <c r="B23" t="n">
-        <v>78455</v>
+        <v>80028</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2838,21 +2833,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>353</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2862,10 +2857,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>583125</v>
+        <v>583092</v>
       </c>
       <c r="R23" t="n">
-        <v>7079741</v>
+        <v>7079777</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -2924,10 +2919,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125412210</v>
+        <v>125410318</v>
       </c>
       <c r="B24" t="n">
-        <v>78810</v>
+        <v>92646</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2940,21 +2935,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>2079</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2964,10 +2959,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>582813</v>
+        <v>583090</v>
       </c>
       <c r="R24" t="n">
-        <v>7079908</v>
+        <v>7079781</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3026,10 +3021,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125412823</v>
+        <v>125409242</v>
       </c>
       <c r="B25" t="n">
-        <v>78810</v>
+        <v>78947</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3066,10 +3061,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>582969</v>
+        <v>582988</v>
       </c>
       <c r="R25" t="n">
-        <v>7079681</v>
+        <v>7079828</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3128,10 +3123,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125409828</v>
+        <v>125408754</v>
       </c>
       <c r="B26" t="n">
-        <v>79891</v>
+        <v>78947</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3144,21 +3139,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3168,10 +3163,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>583020</v>
+        <v>582870</v>
       </c>
       <c r="R26" t="n">
-        <v>7079742</v>
+        <v>7079809</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3230,10 +3225,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125410480</v>
+        <v>125412324</v>
       </c>
       <c r="B27" t="n">
-        <v>78547</v>
+        <v>80056</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3242,25 +3237,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>228912</v>
+        <v>6461</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3270,10 +3265,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>583113</v>
+        <v>582860</v>
       </c>
       <c r="R27" t="n">
-        <v>7079748</v>
+        <v>7079878</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3332,10 +3327,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125412291</v>
+        <v>125412570</v>
       </c>
       <c r="B28" t="n">
-        <v>79891</v>
+        <v>57632</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3348,34 +3343,39 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Omsjöflärken, Omsjöflärken, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>582860</v>
+        <v>582867</v>
       </c>
       <c r="R28" t="n">
-        <v>7079878</v>
+        <v>7079848</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3434,10 +3434,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125410376</v>
+        <v>125412381</v>
       </c>
       <c r="B29" t="n">
-        <v>79891</v>
+        <v>80028</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3474,10 +3474,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>583092</v>
+        <v>582862</v>
       </c>
       <c r="R29" t="n">
-        <v>7079777</v>
+        <v>7079873</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3536,10 +3536,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125409242</v>
+        <v>125412823</v>
       </c>
       <c r="B30" t="n">
-        <v>78810</v>
+        <v>78947</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3576,10 +3576,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>582988</v>
+        <v>582969</v>
       </c>
       <c r="R30" t="n">
-        <v>7079828</v>
+        <v>7079681</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>

--- a/artfynd/A 33964-2023 artfynd.xlsx
+++ b/artfynd/A 33964-2023 artfynd.xlsx
@@ -1797,10 +1797,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125409828</v>
+        <v>125410256</v>
       </c>
       <c r="B13" t="n">
-        <v>80028</v>
+        <v>92448</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1809,25 +1809,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1837,10 +1837,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>583020</v>
+        <v>583089</v>
       </c>
       <c r="R13" t="n">
-        <v>7079742</v>
+        <v>7079781</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1899,10 +1899,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125410256</v>
+        <v>125410683</v>
       </c>
       <c r="B14" t="n">
-        <v>92448</v>
+        <v>78592</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1911,25 +1911,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1939,10 +1939,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>583089</v>
+        <v>583125</v>
       </c>
       <c r="R14" t="n">
-        <v>7079781</v>
+        <v>7079741</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2001,10 +2001,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125410683</v>
+        <v>125410480</v>
       </c>
       <c r="B15" t="n">
-        <v>78592</v>
+        <v>78684</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2017,21 +2017,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2041,10 +2041,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>583125</v>
+        <v>583113</v>
       </c>
       <c r="R15" t="n">
-        <v>7079741</v>
+        <v>7079748</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2103,10 +2103,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125410480</v>
+        <v>125409828</v>
       </c>
       <c r="B16" t="n">
-        <v>78684</v>
+        <v>80028</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2119,21 +2119,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2143,10 +2143,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>583113</v>
+        <v>583020</v>
       </c>
       <c r="R16" t="n">
-        <v>7079748</v>
+        <v>7079742</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -3327,10 +3327,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125412570</v>
+        <v>125412381</v>
       </c>
       <c r="B28" t="n">
-        <v>57632</v>
+        <v>80028</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3343,39 +3343,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Omsjöflärken, Omsjöflärken, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>582867</v>
+        <v>582862</v>
       </c>
       <c r="R28" t="n">
-        <v>7079848</v>
+        <v>7079873</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3434,10 +3429,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125412381</v>
+        <v>125412823</v>
       </c>
       <c r="B29" t="n">
-        <v>80028</v>
+        <v>78947</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3450,21 +3445,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3474,10 +3469,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>582862</v>
+        <v>582969</v>
       </c>
       <c r="R29" t="n">
-        <v>7079873</v>
+        <v>7079681</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3536,10 +3531,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125412823</v>
+        <v>125412570</v>
       </c>
       <c r="B30" t="n">
-        <v>78947</v>
+        <v>57632</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3552,34 +3547,39 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Omsjöflärken, Omsjöflärken, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>582969</v>
+        <v>582867</v>
       </c>
       <c r="R30" t="n">
-        <v>7079681</v>
+        <v>7079848</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>

--- a/artfynd/A 33964-2023 artfynd.xlsx
+++ b/artfynd/A 33964-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125410122</v>
+        <v>125412777</v>
       </c>
       <c r="B2" t="n">
-        <v>92448</v>
+        <v>78947</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>583046</v>
+        <v>582936</v>
       </c>
       <c r="R2" t="n">
-        <v>7079760</v>
+        <v>7079714</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125409866</v>
+        <v>125408929</v>
       </c>
       <c r="B3" t="n">
-        <v>82737</v>
+        <v>91184</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1312</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>583043</v>
+        <v>582879</v>
       </c>
       <c r="R3" t="n">
-        <v>7079761</v>
+        <v>7079836</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -879,7 +879,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125412906</v>
+        <v>125409242</v>
       </c>
       <c r="B4" t="n">
         <v>78947</v>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>582971</v>
+        <v>582988</v>
       </c>
       <c r="R4" t="n">
-        <v>7079630</v>
+        <v>7079828</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125411016</v>
+        <v>125408754</v>
       </c>
       <c r="B5" t="n">
-        <v>78683</v>
+        <v>78947</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>583096</v>
+        <v>582870</v>
       </c>
       <c r="R5" t="n">
-        <v>7079716</v>
+        <v>7079809</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125408990</v>
+        <v>125411016</v>
       </c>
       <c r="B6" t="n">
-        <v>91166</v>
+        <v>78683</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,21 +1099,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>6446</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>582898</v>
+        <v>583096</v>
       </c>
       <c r="R6" t="n">
-        <v>7079836</v>
+        <v>7079716</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125412399</v>
+        <v>125410256</v>
       </c>
       <c r="B7" t="n">
-        <v>80057</v>
+        <v>92448</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,21 +1201,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6462</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>582861</v>
+        <v>583089</v>
       </c>
       <c r="R7" t="n">
-        <v>7079872</v>
+        <v>7079781</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125412291</v>
+        <v>125409301</v>
       </c>
       <c r="B8" t="n">
-        <v>80028</v>
+        <v>80056</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1299,25 +1299,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>6461</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>582860</v>
+        <v>582972</v>
       </c>
       <c r="R8" t="n">
-        <v>7079878</v>
+        <v>7079774</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125409344</v>
+        <v>125409866</v>
       </c>
       <c r="B9" t="n">
-        <v>75025</v>
+        <v>82737</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1405,21 +1405,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6440</v>
+        <v>1312</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>582972</v>
+        <v>583043</v>
       </c>
       <c r="R9" t="n">
-        <v>7079774</v>
+        <v>7079761</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1491,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125412210</v>
+        <v>125408990</v>
       </c>
       <c r="B10" t="n">
-        <v>78947</v>
+        <v>91166</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1507,21 +1507,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>582813</v>
+        <v>582898</v>
       </c>
       <c r="R10" t="n">
-        <v>7079908</v>
+        <v>7079836</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1593,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125409301</v>
+        <v>125412210</v>
       </c>
       <c r="B11" t="n">
-        <v>80056</v>
+        <v>78947</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1605,25 +1605,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1633,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>582972</v>
+        <v>582813</v>
       </c>
       <c r="R11" t="n">
-        <v>7079774</v>
+        <v>7079908</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1695,10 +1695,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125408929</v>
+        <v>125410122</v>
       </c>
       <c r="B12" t="n">
-        <v>91184</v>
+        <v>92448</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1707,25 +1707,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>4364</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1735,10 +1735,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>582879</v>
+        <v>583046</v>
       </c>
       <c r="R12" t="n">
-        <v>7079836</v>
+        <v>7079760</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1797,10 +1797,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125410256</v>
+        <v>125410433</v>
       </c>
       <c r="B13" t="n">
-        <v>92448</v>
+        <v>80028</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1809,25 +1809,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1837,10 +1837,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>583089</v>
+        <v>583110</v>
       </c>
       <c r="R13" t="n">
-        <v>7079781</v>
+        <v>7079768</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1899,10 +1899,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125410683</v>
+        <v>125412570</v>
       </c>
       <c r="B14" t="n">
-        <v>78592</v>
+        <v>57632</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1915,34 +1915,39 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>353</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Omsjöflärken, Omsjöflärken, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>583125</v>
+        <v>582867</v>
       </c>
       <c r="R14" t="n">
-        <v>7079741</v>
+        <v>7079848</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2001,10 +2006,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125410480</v>
+        <v>125408385</v>
       </c>
       <c r="B15" t="n">
-        <v>78684</v>
+        <v>78947</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2017,21 +2022,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2041,10 +2046,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>583113</v>
+        <v>582906</v>
       </c>
       <c r="R15" t="n">
-        <v>7079748</v>
+        <v>7079758</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2103,10 +2108,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125409828</v>
+        <v>125412324</v>
       </c>
       <c r="B16" t="n">
-        <v>80028</v>
+        <v>80056</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2115,25 +2120,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>6461</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2143,10 +2148,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>583020</v>
+        <v>582860</v>
       </c>
       <c r="R16" t="n">
-        <v>7079742</v>
+        <v>7079878</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2307,10 +2312,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125410433</v>
+        <v>125412823</v>
       </c>
       <c r="B18" t="n">
-        <v>80028</v>
+        <v>78947</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2323,21 +2328,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2347,10 +2352,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>583110</v>
+        <v>582969</v>
       </c>
       <c r="R18" t="n">
-        <v>7079768</v>
+        <v>7079681</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2409,10 +2414,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125412777</v>
+        <v>125412399</v>
       </c>
       <c r="B19" t="n">
-        <v>78947</v>
+        <v>80057</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2421,25 +2426,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2449,10 +2454,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>582936</v>
+        <v>582861</v>
       </c>
       <c r="R19" t="n">
-        <v>7079714</v>
+        <v>7079872</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2511,7 +2516,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125412758</v>
+        <v>125412381</v>
       </c>
       <c r="B20" t="n">
         <v>80028</v>
@@ -2551,10 +2556,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>582922</v>
+        <v>582862</v>
       </c>
       <c r="R20" t="n">
-        <v>7079716</v>
+        <v>7079873</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2715,10 +2720,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125408385</v>
+        <v>125410683</v>
       </c>
       <c r="B22" t="n">
-        <v>78947</v>
+        <v>78592</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2731,21 +2736,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2755,10 +2760,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>582906</v>
+        <v>583125</v>
       </c>
       <c r="R22" t="n">
-        <v>7079758</v>
+        <v>7079741</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2919,10 +2924,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125410318</v>
+        <v>125412758</v>
       </c>
       <c r="B24" t="n">
-        <v>92646</v>
+        <v>80028</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2935,21 +2940,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2079</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2959,10 +2964,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>583090</v>
+        <v>582922</v>
       </c>
       <c r="R24" t="n">
-        <v>7079781</v>
+        <v>7079716</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3021,7 +3026,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125409242</v>
+        <v>125412906</v>
       </c>
       <c r="B25" t="n">
         <v>78947</v>
@@ -3061,10 +3066,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>582988</v>
+        <v>582971</v>
       </c>
       <c r="R25" t="n">
-        <v>7079828</v>
+        <v>7079630</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3123,10 +3128,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125408754</v>
+        <v>125409344</v>
       </c>
       <c r="B26" t="n">
-        <v>78947</v>
+        <v>75025</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3139,21 +3144,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3163,10 +3168,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>582870</v>
+        <v>582972</v>
       </c>
       <c r="R26" t="n">
-        <v>7079809</v>
+        <v>7079774</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3225,10 +3230,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125412324</v>
+        <v>125412291</v>
       </c>
       <c r="B27" t="n">
-        <v>80056</v>
+        <v>80028</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3237,25 +3242,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6461</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3327,7 +3332,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125412381</v>
+        <v>125409828</v>
       </c>
       <c r="B28" t="n">
         <v>80028</v>
@@ -3367,10 +3372,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>582862</v>
+        <v>583020</v>
       </c>
       <c r="R28" t="n">
-        <v>7079873</v>
+        <v>7079742</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3429,10 +3434,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125412823</v>
+        <v>125410318</v>
       </c>
       <c r="B29" t="n">
-        <v>78947</v>
+        <v>92646</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3445,21 +3450,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>2079</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3469,10 +3474,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>582969</v>
+        <v>583090</v>
       </c>
       <c r="R29" t="n">
-        <v>7079681</v>
+        <v>7079781</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3531,10 +3536,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125412570</v>
+        <v>125410480</v>
       </c>
       <c r="B30" t="n">
-        <v>57632</v>
+        <v>78684</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3547,39 +3552,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Omsjöflärken, Omsjöflärken, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>582867</v>
+        <v>583113</v>
       </c>
       <c r="R30" t="n">
-        <v>7079848</v>
+        <v>7079748</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>

--- a/artfynd/A 33964-2023 artfynd.xlsx
+++ b/artfynd/A 33964-2023 artfynd.xlsx
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125409866</v>
+        <v>125412210</v>
       </c>
       <c r="B9" t="n">
-        <v>82737</v>
+        <v>78947</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1405,21 +1405,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>583043</v>
+        <v>582813</v>
       </c>
       <c r="R9" t="n">
-        <v>7079761</v>
+        <v>7079908</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1491,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125408990</v>
+        <v>125409866</v>
       </c>
       <c r="B10" t="n">
-        <v>91166</v>
+        <v>82737</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1507,21 +1507,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>582898</v>
+        <v>583043</v>
       </c>
       <c r="R10" t="n">
-        <v>7079836</v>
+        <v>7079761</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1593,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125412210</v>
+        <v>125408990</v>
       </c>
       <c r="B11" t="n">
-        <v>78947</v>
+        <v>91166</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1609,21 +1609,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1633,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>582813</v>
+        <v>582898</v>
       </c>
       <c r="R11" t="n">
-        <v>7079908</v>
+        <v>7079836</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>

--- a/artfynd/A 33964-2023 artfynd.xlsx
+++ b/artfynd/A 33964-2023 artfynd.xlsx
@@ -1899,10 +1899,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125412570</v>
+        <v>125408385</v>
       </c>
       <c r="B14" t="n">
-        <v>57632</v>
+        <v>78947</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1915,39 +1915,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Omsjöflärken, Omsjöflärken, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>582867</v>
+        <v>582906</v>
       </c>
       <c r="R14" t="n">
-        <v>7079848</v>
+        <v>7079758</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2006,10 +2001,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125408385</v>
+        <v>125412570</v>
       </c>
       <c r="B15" t="n">
-        <v>78947</v>
+        <v>57632</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2022,34 +2017,39 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Omsjöflärken, Omsjöflärken, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>582906</v>
+        <v>582867</v>
       </c>
       <c r="R15" t="n">
-        <v>7079758</v>
+        <v>7079848</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>

--- a/artfynd/A 33964-2023 artfynd.xlsx
+++ b/artfynd/A 33964-2023 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125412777</v>
+        <v>125412570</v>
       </c>
       <c r="B2" t="n">
-        <v>78947</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57648</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,34 +686,39 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Omsjöflärken, Omsjöflärken, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>582936</v>
+        <v>582867</v>
       </c>
       <c r="R2" t="n">
-        <v>7079714</v>
+        <v>7079848</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -777,15 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125408929</v>
+        <v>125409866</v>
       </c>
       <c r="B3" t="n">
-        <v>91184</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>82779</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,21 +788,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>1312</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>582879</v>
+        <v>583043</v>
       </c>
       <c r="R3" t="n">
-        <v>7079836</v>
+        <v>7079761</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -879,15 +874,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125409242</v>
+        <v>125408990</v>
       </c>
       <c r="B4" t="n">
-        <v>78947</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91220</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -895,21 +885,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +909,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>582988</v>
+        <v>582898</v>
       </c>
       <c r="R4" t="n">
-        <v>7079828</v>
+        <v>7079836</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -981,15 +971,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125408754</v>
+        <v>125411016</v>
       </c>
       <c r="B5" t="n">
-        <v>78947</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78725</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -997,21 +982,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1006,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>582870</v>
+        <v>583096</v>
       </c>
       <c r="R5" t="n">
-        <v>7079809</v>
+        <v>7079716</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1083,15 +1068,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125411016</v>
+        <v>125412381</v>
       </c>
       <c r="B6" t="n">
-        <v>78683</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80070</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1099,21 +1079,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1103,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>583096</v>
+        <v>582862</v>
       </c>
       <c r="R6" t="n">
-        <v>7079716</v>
+        <v>7079873</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1185,37 +1165,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125410256</v>
+        <v>125408929</v>
       </c>
       <c r="B7" t="n">
-        <v>92448</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91238</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4364</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1200,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>583089</v>
+        <v>582879</v>
       </c>
       <c r="R7" t="n">
-        <v>7079781</v>
+        <v>7079836</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1287,37 +1262,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125409301</v>
+        <v>125412210</v>
       </c>
       <c r="B8" t="n">
-        <v>80056</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78967</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1297,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>582972</v>
+        <v>582813</v>
       </c>
       <c r="R8" t="n">
-        <v>7079774</v>
+        <v>7079908</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1389,15 +1359,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125412210</v>
+        <v>125409899</v>
       </c>
       <c r="B9" t="n">
-        <v>78947</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78967</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1429,10 +1394,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>582813</v>
+        <v>583044</v>
       </c>
       <c r="R9" t="n">
-        <v>7079908</v>
+        <v>7079761</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1491,15 +1456,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125409866</v>
+        <v>125410433</v>
       </c>
       <c r="B10" t="n">
-        <v>82737</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80070</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1507,21 +1467,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1312</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1531,10 +1491,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>583043</v>
+        <v>583110</v>
       </c>
       <c r="R10" t="n">
-        <v>7079761</v>
+        <v>7079768</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1593,15 +1553,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125408990</v>
+        <v>125410480</v>
       </c>
       <c r="B11" t="n">
-        <v>91166</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78726</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1609,21 +1564,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>228912</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1633,10 +1588,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>582898</v>
+        <v>583113</v>
       </c>
       <c r="R11" t="n">
-        <v>7079836</v>
+        <v>7079748</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1695,37 +1650,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125410122</v>
+        <v>125409242</v>
       </c>
       <c r="B12" t="n">
-        <v>92448</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78967</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1735,10 +1685,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>583046</v>
+        <v>582988</v>
       </c>
       <c r="R12" t="n">
-        <v>7079760</v>
+        <v>7079828</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1797,15 +1747,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125410433</v>
+        <v>125412777</v>
       </c>
       <c r="B13" t="n">
-        <v>80028</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78967</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1813,21 +1758,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1837,10 +1782,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>583110</v>
+        <v>582936</v>
       </c>
       <c r="R13" t="n">
-        <v>7079768</v>
+        <v>7079714</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1899,37 +1844,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125408385</v>
+        <v>125410122</v>
       </c>
       <c r="B14" t="n">
-        <v>78947</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92502</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1939,10 +1879,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>582906</v>
+        <v>583046</v>
       </c>
       <c r="R14" t="n">
-        <v>7079758</v>
+        <v>7079760</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2001,15 +1941,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125412570</v>
+        <v>125408385</v>
       </c>
       <c r="B15" t="n">
-        <v>57632</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78967</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2017,39 +1952,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Omsjöflärken, Omsjöflärken, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>582867</v>
+        <v>582906</v>
       </c>
       <c r="R15" t="n">
-        <v>7079848</v>
+        <v>7079758</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2111,12 +2041,7 @@
         <v>125412324</v>
       </c>
       <c r="B16" t="n">
-        <v>80056</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80098</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2210,15 +2135,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125409899</v>
+        <v>125408754</v>
       </c>
       <c r="B17" t="n">
-        <v>78947</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78967</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2250,10 +2170,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>583044</v>
+        <v>582870</v>
       </c>
       <c r="R17" t="n">
-        <v>7079761</v>
+        <v>7079809</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2312,15 +2232,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125412823</v>
+        <v>125410683</v>
       </c>
       <c r="B18" t="n">
-        <v>78947</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78634</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2328,21 +2243,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2352,10 +2267,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>582969</v>
+        <v>583125</v>
       </c>
       <c r="R18" t="n">
-        <v>7079681</v>
+        <v>7079741</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2414,37 +2329,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125412399</v>
+        <v>125412291</v>
       </c>
       <c r="B19" t="n">
-        <v>80057</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80070</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2454,10 +2364,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>582861</v>
+        <v>582860</v>
       </c>
       <c r="R19" t="n">
-        <v>7079872</v>
+        <v>7079878</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2516,15 +2426,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125412381</v>
+        <v>125412906</v>
       </c>
       <c r="B20" t="n">
-        <v>80028</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78967</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2532,21 +2437,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2556,10 +2461,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>582862</v>
+        <v>582971</v>
       </c>
       <c r="R20" t="n">
-        <v>7079873</v>
+        <v>7079630</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2618,15 +2523,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125412472</v>
+        <v>125410376</v>
       </c>
       <c r="B21" t="n">
-        <v>78947</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80070</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2634,21 +2534,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2658,10 +2558,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>582841</v>
+        <v>583092</v>
       </c>
       <c r="R21" t="n">
-        <v>7079874</v>
+        <v>7079777</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2720,15 +2620,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125410683</v>
+        <v>125412758</v>
       </c>
       <c r="B22" t="n">
-        <v>78592</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80070</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2736,21 +2631,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>353</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2760,10 +2655,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>583125</v>
+        <v>582922</v>
       </c>
       <c r="R22" t="n">
-        <v>7079741</v>
+        <v>7079716</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2822,15 +2717,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125410376</v>
+        <v>125412823</v>
       </c>
       <c r="B23" t="n">
-        <v>80028</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78967</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2838,21 +2728,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2862,10 +2752,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>583092</v>
+        <v>582969</v>
       </c>
       <c r="R23" t="n">
-        <v>7079777</v>
+        <v>7079681</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -2924,37 +2814,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125412758</v>
+        <v>125412399</v>
       </c>
       <c r="B24" t="n">
-        <v>80028</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80099</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2964,10 +2849,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>582922</v>
+        <v>582861</v>
       </c>
       <c r="R24" t="n">
-        <v>7079716</v>
+        <v>7079872</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3026,37 +2911,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125412906</v>
+        <v>125410256</v>
       </c>
       <c r="B25" t="n">
-        <v>78947</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92502</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3066,10 +2946,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>582971</v>
+        <v>583089</v>
       </c>
       <c r="R25" t="n">
-        <v>7079630</v>
+        <v>7079781</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3128,15 +3008,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125409344</v>
+        <v>125409828</v>
       </c>
       <c r="B26" t="n">
-        <v>75025</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80070</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3144,21 +3019,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6440</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3168,10 +3043,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>582972</v>
+        <v>583020</v>
       </c>
       <c r="R26" t="n">
-        <v>7079774</v>
+        <v>7079742</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3230,15 +3105,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125412291</v>
+        <v>125410318</v>
       </c>
       <c r="B27" t="n">
-        <v>80028</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92700</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3246,21 +3116,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6458</v>
+        <v>2079</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3270,10 +3140,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>582860</v>
+        <v>583090</v>
       </c>
       <c r="R27" t="n">
-        <v>7079878</v>
+        <v>7079781</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3332,15 +3202,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125409828</v>
+        <v>125409344</v>
       </c>
       <c r="B28" t="n">
-        <v>80028</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75066</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3348,21 +3213,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3372,10 +3237,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>583020</v>
+        <v>582972</v>
       </c>
       <c r="R28" t="n">
-        <v>7079742</v>
+        <v>7079774</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3434,37 +3299,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125410318</v>
+        <v>125409301</v>
       </c>
       <c r="B29" t="n">
-        <v>92646</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80098</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2079</v>
+        <v>6461</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3474,10 +3334,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>583090</v>
+        <v>582972</v>
       </c>
       <c r="R29" t="n">
-        <v>7079781</v>
+        <v>7079774</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3536,15 +3396,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125410480</v>
+        <v>125412472</v>
       </c>
       <c r="B30" t="n">
-        <v>78684</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78967</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3552,21 +3407,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3576,10 +3431,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>583113</v>
+        <v>582841</v>
       </c>
       <c r="R30" t="n">
-        <v>7079748</v>
+        <v>7079874</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>

--- a/artfynd/A 33964-2023 artfynd.xlsx
+++ b/artfynd/A 33964-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125412570</v>
+        <v>125409866</v>
       </c>
       <c r="B2" t="n">
-        <v>57648</v>
+        <v>82779</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,39 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>1312</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Omsjöflärken, Omsjöflärken, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>582867</v>
+        <v>583043</v>
       </c>
       <c r="R2" t="n">
-        <v>7079848</v>
+        <v>7079761</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -777,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125409866</v>
+        <v>125408990</v>
       </c>
       <c r="B3" t="n">
-        <v>82779</v>
+        <v>91220</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -788,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -812,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>583043</v>
+        <v>582898</v>
       </c>
       <c r="R3" t="n">
-        <v>7079761</v>
+        <v>7079836</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -874,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125408990</v>
+        <v>125412570</v>
       </c>
       <c r="B4" t="n">
-        <v>91220</v>
+        <v>57648</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -885,34 +880,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Omsjöflärken, Omsjöflärken, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>582898</v>
+        <v>582867</v>
       </c>
       <c r="R4" t="n">
-        <v>7079836</v>
+        <v>7079848</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -1359,10 +1359,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125409899</v>
+        <v>125410480</v>
       </c>
       <c r="B9" t="n">
-        <v>78967</v>
+        <v>78726</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1370,21 +1370,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1394,10 +1394,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>583044</v>
+        <v>583113</v>
       </c>
       <c r="R9" t="n">
-        <v>7079761</v>
+        <v>7079748</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1456,10 +1456,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125410433</v>
+        <v>125409899</v>
       </c>
       <c r="B10" t="n">
-        <v>80070</v>
+        <v>78967</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1467,21 +1467,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1491,10 +1491,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>583110</v>
+        <v>583044</v>
       </c>
       <c r="R10" t="n">
-        <v>7079768</v>
+        <v>7079761</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1553,10 +1553,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125410480</v>
+        <v>125410433</v>
       </c>
       <c r="B11" t="n">
-        <v>78726</v>
+        <v>80070</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1564,21 +1564,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1588,10 +1588,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>583113</v>
+        <v>583110</v>
       </c>
       <c r="R11" t="n">
-        <v>7079748</v>
+        <v>7079768</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>

--- a/artfynd/A 33964-2023 artfynd.xlsx
+++ b/artfynd/A 33964-2023 artfynd.xlsx
@@ -775,7 +775,7 @@
         <v>125408990</v>
       </c>
       <c r="B3" t="n">
-        <v>91220</v>
+        <v>91227</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1168,7 +1168,7 @@
         <v>125408929</v>
       </c>
       <c r="B7" t="n">
-        <v>91238</v>
+        <v>91245</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1359,10 +1359,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125410480</v>
+        <v>125409899</v>
       </c>
       <c r="B9" t="n">
-        <v>78726</v>
+        <v>78967</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1370,21 +1370,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1394,10 +1394,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>583113</v>
+        <v>583044</v>
       </c>
       <c r="R9" t="n">
-        <v>7079748</v>
+        <v>7079761</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1456,10 +1456,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125409899</v>
+        <v>125410433</v>
       </c>
       <c r="B10" t="n">
-        <v>78967</v>
+        <v>80070</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1467,21 +1467,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1491,10 +1491,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>583044</v>
+        <v>583110</v>
       </c>
       <c r="R10" t="n">
-        <v>7079761</v>
+        <v>7079768</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1553,10 +1553,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125410433</v>
+        <v>125410480</v>
       </c>
       <c r="B11" t="n">
-        <v>80070</v>
+        <v>78726</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1564,21 +1564,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1588,10 +1588,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>583110</v>
+        <v>583113</v>
       </c>
       <c r="R11" t="n">
-        <v>7079768</v>
+        <v>7079748</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1844,32 +1844,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125410122</v>
+        <v>125408385</v>
       </c>
       <c r="B14" t="n">
-        <v>92502</v>
+        <v>78967</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1879,10 +1879,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>583046</v>
+        <v>582906</v>
       </c>
       <c r="R14" t="n">
-        <v>7079760</v>
+        <v>7079758</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -1941,32 +1941,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125408385</v>
+        <v>125410122</v>
       </c>
       <c r="B15" t="n">
-        <v>78967</v>
+        <v>92509</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1976,10 +1976,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>582906</v>
+        <v>583046</v>
       </c>
       <c r="R15" t="n">
-        <v>7079758</v>
+        <v>7079760</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2135,10 +2135,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125408754</v>
+        <v>125410683</v>
       </c>
       <c r="B17" t="n">
-        <v>78967</v>
+        <v>78634</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2146,21 +2146,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2170,10 +2170,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>582870</v>
+        <v>583125</v>
       </c>
       <c r="R17" t="n">
-        <v>7079809</v>
+        <v>7079741</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2232,10 +2232,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125410683</v>
+        <v>125408754</v>
       </c>
       <c r="B18" t="n">
-        <v>78634</v>
+        <v>78967</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2243,21 +2243,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2267,10 +2267,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>583125</v>
+        <v>582870</v>
       </c>
       <c r="R18" t="n">
-        <v>7079741</v>
+        <v>7079809</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2911,32 +2911,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125410256</v>
+        <v>125410318</v>
       </c>
       <c r="B25" t="n">
-        <v>92502</v>
+        <v>92707</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4364</v>
+        <v>2079</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2946,7 +2946,7 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>583089</v>
+        <v>583090</v>
       </c>
       <c r="R25" t="n">
         <v>7079781</v>
@@ -3008,32 +3008,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125409828</v>
+        <v>125410256</v>
       </c>
       <c r="B26" t="n">
-        <v>80070</v>
+        <v>92509</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3043,10 +3043,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>583020</v>
+        <v>583089</v>
       </c>
       <c r="R26" t="n">
-        <v>7079742</v>
+        <v>7079781</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3105,10 +3105,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125410318</v>
+        <v>125409828</v>
       </c>
       <c r="B27" t="n">
-        <v>92700</v>
+        <v>80070</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3116,21 +3116,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2079</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3140,10 +3140,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>583090</v>
+        <v>583020</v>
       </c>
       <c r="R27" t="n">
-        <v>7079781</v>
+        <v>7079742</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>

--- a/artfynd/A 33964-2023 artfynd.xlsx
+++ b/artfynd/A 33964-2023 artfynd.xlsx
@@ -1844,32 +1844,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125408385</v>
+        <v>125410122</v>
       </c>
       <c r="B14" t="n">
-        <v>78967</v>
+        <v>92509</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1879,10 +1879,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>582906</v>
+        <v>583046</v>
       </c>
       <c r="R14" t="n">
-        <v>7079758</v>
+        <v>7079760</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -1941,32 +1941,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125410122</v>
+        <v>125408385</v>
       </c>
       <c r="B15" t="n">
-        <v>92509</v>
+        <v>78967</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1976,10 +1976,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>583046</v>
+        <v>582906</v>
       </c>
       <c r="R15" t="n">
-        <v>7079760</v>
+        <v>7079758</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>

--- a/artfynd/A 33964-2023 artfynd.xlsx
+++ b/artfynd/A 33964-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125409866</v>
+        <v>125412570</v>
       </c>
       <c r="B2" t="n">
-        <v>82779</v>
+        <v>57648</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,39 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1312</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Omsjöflärken, Omsjöflärken, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>583043</v>
+        <v>582867</v>
       </c>
       <c r="R2" t="n">
-        <v>7079761</v>
+        <v>7079848</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -772,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125408990</v>
+        <v>125409866</v>
       </c>
       <c r="B3" t="n">
-        <v>91227</v>
+        <v>82780</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +788,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>582898</v>
+        <v>583043</v>
       </c>
       <c r="R3" t="n">
-        <v>7079836</v>
+        <v>7079761</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -869,10 +874,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125412570</v>
+        <v>125408990</v>
       </c>
       <c r="B4" t="n">
-        <v>57648</v>
+        <v>91228</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,39 +885,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Omsjöflärken, Omsjöflärken, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>582867</v>
+        <v>582898</v>
       </c>
       <c r="R4" t="n">
-        <v>7079848</v>
+        <v>7079836</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -974,7 +974,7 @@
         <v>125411016</v>
       </c>
       <c r="B5" t="n">
-        <v>78725</v>
+        <v>78726</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
         <v>125412381</v>
       </c>
       <c r="B6" t="n">
-        <v>80070</v>
+        <v>80071</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1168,7 +1168,7 @@
         <v>125408929</v>
       </c>
       <c r="B7" t="n">
-        <v>91245</v>
+        <v>91246</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1265,7 +1265,7 @@
         <v>125412210</v>
       </c>
       <c r="B8" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1359,10 +1359,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125409899</v>
+        <v>125410480</v>
       </c>
       <c r="B9" t="n">
-        <v>78967</v>
+        <v>78727</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1370,21 +1370,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1394,10 +1394,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>583044</v>
+        <v>583113</v>
       </c>
       <c r="R9" t="n">
-        <v>7079761</v>
+        <v>7079748</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1459,7 +1459,7 @@
         <v>125410433</v>
       </c>
       <c r="B10" t="n">
-        <v>80070</v>
+        <v>80071</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1553,10 +1553,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125410480</v>
+        <v>125409899</v>
       </c>
       <c r="B11" t="n">
-        <v>78726</v>
+        <v>78968</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1564,21 +1564,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1588,10 +1588,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>583113</v>
+        <v>583044</v>
       </c>
       <c r="R11" t="n">
-        <v>7079748</v>
+        <v>7079761</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1650,10 +1650,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125409242</v>
+        <v>125412777</v>
       </c>
       <c r="B12" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1685,10 +1685,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>582988</v>
+        <v>582936</v>
       </c>
       <c r="R12" t="n">
-        <v>7079828</v>
+        <v>7079714</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1747,10 +1747,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125412777</v>
+        <v>125409242</v>
       </c>
       <c r="B13" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1782,10 +1782,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>582936</v>
+        <v>582988</v>
       </c>
       <c r="R13" t="n">
-        <v>7079714</v>
+        <v>7079828</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1847,7 +1847,7 @@
         <v>125410122</v>
       </c>
       <c r="B14" t="n">
-        <v>92509</v>
+        <v>92518</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1944,7 +1944,7 @@
         <v>125408385</v>
       </c>
       <c r="B15" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2041,7 +2041,7 @@
         <v>125412324</v>
       </c>
       <c r="B16" t="n">
-        <v>80098</v>
+        <v>80099</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2138,7 +2138,7 @@
         <v>125410683</v>
       </c>
       <c r="B17" t="n">
-        <v>78634</v>
+        <v>78635</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2235,7 +2235,7 @@
         <v>125408754</v>
       </c>
       <c r="B18" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2332,7 +2332,7 @@
         <v>125412291</v>
       </c>
       <c r="B19" t="n">
-        <v>80070</v>
+        <v>80071</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2429,7 +2429,7 @@
         <v>125412906</v>
       </c>
       <c r="B20" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2526,7 +2526,7 @@
         <v>125410376</v>
       </c>
       <c r="B21" t="n">
-        <v>80070</v>
+        <v>80071</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2620,10 +2620,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125412758</v>
+        <v>125412823</v>
       </c>
       <c r="B22" t="n">
-        <v>80070</v>
+        <v>78968</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2631,21 +2631,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2655,10 +2655,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>582922</v>
+        <v>582969</v>
       </c>
       <c r="R22" t="n">
-        <v>7079716</v>
+        <v>7079681</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2717,10 +2717,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125412823</v>
+        <v>125412758</v>
       </c>
       <c r="B23" t="n">
-        <v>78967</v>
+        <v>80071</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2728,21 +2728,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2752,10 +2752,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>582969</v>
+        <v>582922</v>
       </c>
       <c r="R23" t="n">
-        <v>7079681</v>
+        <v>7079716</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -2817,7 +2817,7 @@
         <v>125412399</v>
       </c>
       <c r="B24" t="n">
-        <v>80099</v>
+        <v>80100</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2914,7 +2914,7 @@
         <v>125410318</v>
       </c>
       <c r="B25" t="n">
-        <v>92707</v>
+        <v>92710</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3011,7 +3011,7 @@
         <v>125410256</v>
       </c>
       <c r="B26" t="n">
-        <v>92509</v>
+        <v>92518</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3108,7 +3108,7 @@
         <v>125409828</v>
       </c>
       <c r="B27" t="n">
-        <v>80070</v>
+        <v>80071</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3205,7 +3205,7 @@
         <v>125409344</v>
       </c>
       <c r="B28" t="n">
-        <v>75066</v>
+        <v>75067</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3302,7 +3302,7 @@
         <v>125409301</v>
       </c>
       <c r="B29" t="n">
-        <v>80098</v>
+        <v>80099</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3399,7 +3399,7 @@
         <v>125412472</v>
       </c>
       <c r="B30" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 33964-2023 artfynd.xlsx
+++ b/artfynd/A 33964-2023 artfynd.xlsx
@@ -1359,10 +1359,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125410480</v>
+        <v>125410433</v>
       </c>
       <c r="B9" t="n">
-        <v>78727</v>
+        <v>80071</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1370,21 +1370,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1394,10 +1394,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>583113</v>
+        <v>583110</v>
       </c>
       <c r="R9" t="n">
-        <v>7079748</v>
+        <v>7079768</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1456,10 +1456,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125410433</v>
+        <v>125409899</v>
       </c>
       <c r="B10" t="n">
-        <v>80071</v>
+        <v>78968</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1467,21 +1467,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1491,10 +1491,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>583110</v>
+        <v>583044</v>
       </c>
       <c r="R10" t="n">
-        <v>7079768</v>
+        <v>7079761</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1553,10 +1553,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125409899</v>
+        <v>125410480</v>
       </c>
       <c r="B11" t="n">
-        <v>78968</v>
+        <v>78727</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1564,21 +1564,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1588,10 +1588,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>583044</v>
+        <v>583113</v>
       </c>
       <c r="R11" t="n">
-        <v>7079761</v>
+        <v>7079748</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>

--- a/artfynd/A 33964-2023 artfynd.xlsx
+++ b/artfynd/A 33964-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125412570</v>
+        <v>125409866</v>
       </c>
       <c r="B2" t="n">
-        <v>57648</v>
+        <v>82784</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,39 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>1312</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Omsjöflärken, Omsjöflärken, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>582867</v>
+        <v>583043</v>
       </c>
       <c r="R2" t="n">
-        <v>7079848</v>
+        <v>7079761</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -777,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125409866</v>
+        <v>125408990</v>
       </c>
       <c r="B3" t="n">
-        <v>82780</v>
+        <v>91232</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -788,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -812,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>583043</v>
+        <v>582898</v>
       </c>
       <c r="R3" t="n">
-        <v>7079761</v>
+        <v>7079836</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -874,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125408990</v>
+        <v>125412570</v>
       </c>
       <c r="B4" t="n">
-        <v>91228</v>
+        <v>57648</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -885,34 +880,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Omsjöflärken, Omsjöflärken, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>582898</v>
+        <v>582867</v>
       </c>
       <c r="R4" t="n">
-        <v>7079836</v>
+        <v>7079848</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -974,7 +974,7 @@
         <v>125411016</v>
       </c>
       <c r="B5" t="n">
-        <v>78726</v>
+        <v>78730</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
         <v>125412381</v>
       </c>
       <c r="B6" t="n">
-        <v>80071</v>
+        <v>80075</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1168,7 +1168,7 @@
         <v>125408929</v>
       </c>
       <c r="B7" t="n">
-        <v>91246</v>
+        <v>91250</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1265,7 +1265,7 @@
         <v>125412210</v>
       </c>
       <c r="B8" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1362,7 +1362,7 @@
         <v>125410433</v>
       </c>
       <c r="B9" t="n">
-        <v>80071</v>
+        <v>80075</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1459,7 +1459,7 @@
         <v>125409899</v>
       </c>
       <c r="B10" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1556,7 +1556,7 @@
         <v>125410480</v>
       </c>
       <c r="B11" t="n">
-        <v>78727</v>
+        <v>78731</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1653,7 +1653,7 @@
         <v>125412777</v>
       </c>
       <c r="B12" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1750,7 +1750,7 @@
         <v>125409242</v>
       </c>
       <c r="B13" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1844,32 +1844,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125410122</v>
+        <v>125408385</v>
       </c>
       <c r="B14" t="n">
-        <v>92518</v>
+        <v>78972</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1879,10 +1879,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>583046</v>
+        <v>582906</v>
       </c>
       <c r="R14" t="n">
-        <v>7079760</v>
+        <v>7079758</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -1941,32 +1941,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125408385</v>
+        <v>125410122</v>
       </c>
       <c r="B15" t="n">
-        <v>78968</v>
+        <v>92522</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1976,10 +1976,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>582906</v>
+        <v>583046</v>
       </c>
       <c r="R15" t="n">
-        <v>7079758</v>
+        <v>7079760</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2041,7 +2041,7 @@
         <v>125412324</v>
       </c>
       <c r="B16" t="n">
-        <v>80099</v>
+        <v>80103</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2135,10 +2135,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125410683</v>
+        <v>125408754</v>
       </c>
       <c r="B17" t="n">
-        <v>78635</v>
+        <v>78972</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2146,21 +2146,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2170,10 +2170,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>583125</v>
+        <v>582870</v>
       </c>
       <c r="R17" t="n">
-        <v>7079741</v>
+        <v>7079809</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2232,10 +2232,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125408754</v>
+        <v>125410683</v>
       </c>
       <c r="B18" t="n">
-        <v>78968</v>
+        <v>78639</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2243,21 +2243,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2267,10 +2267,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>582870</v>
+        <v>583125</v>
       </c>
       <c r="R18" t="n">
-        <v>7079809</v>
+        <v>7079741</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2332,7 +2332,7 @@
         <v>125412291</v>
       </c>
       <c r="B19" t="n">
-        <v>80071</v>
+        <v>80075</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2429,7 +2429,7 @@
         <v>125412906</v>
       </c>
       <c r="B20" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2526,7 +2526,7 @@
         <v>125410376</v>
       </c>
       <c r="B21" t="n">
-        <v>80071</v>
+        <v>80075</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2623,7 +2623,7 @@
         <v>125412823</v>
       </c>
       <c r="B22" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2720,7 +2720,7 @@
         <v>125412758</v>
       </c>
       <c r="B23" t="n">
-        <v>80071</v>
+        <v>80075</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2817,7 +2817,7 @@
         <v>125412399</v>
       </c>
       <c r="B24" t="n">
-        <v>80100</v>
+        <v>80104</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2914,7 +2914,7 @@
         <v>125410318</v>
       </c>
       <c r="B25" t="n">
-        <v>92710</v>
+        <v>92714</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3008,32 +3008,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125410256</v>
+        <v>125409828</v>
       </c>
       <c r="B26" t="n">
-        <v>92518</v>
+        <v>80075</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3043,10 +3043,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>583089</v>
+        <v>583020</v>
       </c>
       <c r="R26" t="n">
-        <v>7079781</v>
+        <v>7079742</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3105,32 +3105,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125409828</v>
+        <v>125410256</v>
       </c>
       <c r="B27" t="n">
-        <v>80071</v>
+        <v>92522</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3140,10 +3140,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>583020</v>
+        <v>583089</v>
       </c>
       <c r="R27" t="n">
-        <v>7079742</v>
+        <v>7079781</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3202,32 +3202,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125409344</v>
+        <v>125409301</v>
       </c>
       <c r="B28" t="n">
-        <v>75067</v>
+        <v>80103</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6440</v>
+        <v>6461</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3299,32 +3299,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125409301</v>
+        <v>125409344</v>
       </c>
       <c r="B29" t="n">
-        <v>80099</v>
+        <v>75067</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6461</v>
+        <v>6440</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3399,7 +3399,7 @@
         <v>125412472</v>
       </c>
       <c r="B30" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 33964-2023 artfynd.xlsx
+++ b/artfynd/A 33964-2023 artfynd.xlsx
@@ -1844,32 +1844,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125408385</v>
+        <v>125410122</v>
       </c>
       <c r="B14" t="n">
-        <v>78972</v>
+        <v>92522</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1879,10 +1879,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>582906</v>
+        <v>583046</v>
       </c>
       <c r="R14" t="n">
-        <v>7079758</v>
+        <v>7079760</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -1941,32 +1941,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125410122</v>
+        <v>125408385</v>
       </c>
       <c r="B15" t="n">
-        <v>92522</v>
+        <v>78972</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1976,10 +1976,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>583046</v>
+        <v>582906</v>
       </c>
       <c r="R15" t="n">
-        <v>7079760</v>
+        <v>7079758</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>

--- a/artfynd/A 33964-2023 artfynd.xlsx
+++ b/artfynd/A 33964-2023 artfynd.xlsx
@@ -1359,10 +1359,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125410433</v>
+        <v>125410480</v>
       </c>
       <c r="B9" t="n">
-        <v>80075</v>
+        <v>78731</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1370,21 +1370,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1394,10 +1394,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>583110</v>
+        <v>583113</v>
       </c>
       <c r="R9" t="n">
-        <v>7079768</v>
+        <v>7079748</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1553,10 +1553,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125410480</v>
+        <v>125410433</v>
       </c>
       <c r="B11" t="n">
-        <v>78731</v>
+        <v>80075</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1564,21 +1564,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1588,10 +1588,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>583113</v>
+        <v>583110</v>
       </c>
       <c r="R11" t="n">
-        <v>7079748</v>
+        <v>7079768</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1650,7 +1650,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125412777</v>
+        <v>125409242</v>
       </c>
       <c r="B12" t="n">
         <v>78972</v>
@@ -1685,10 +1685,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>582936</v>
+        <v>582988</v>
       </c>
       <c r="R12" t="n">
-        <v>7079714</v>
+        <v>7079828</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1747,7 +1747,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125409242</v>
+        <v>125412777</v>
       </c>
       <c r="B13" t="n">
         <v>78972</v>
@@ -1782,10 +1782,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>582988</v>
+        <v>582936</v>
       </c>
       <c r="R13" t="n">
-        <v>7079828</v>
+        <v>7079714</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -2135,10 +2135,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125408754</v>
+        <v>125410683</v>
       </c>
       <c r="B17" t="n">
-        <v>78972</v>
+        <v>78639</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2146,21 +2146,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2170,10 +2170,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>582870</v>
+        <v>583125</v>
       </c>
       <c r="R17" t="n">
-        <v>7079809</v>
+        <v>7079741</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2232,10 +2232,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125410683</v>
+        <v>125408754</v>
       </c>
       <c r="B18" t="n">
-        <v>78639</v>
+        <v>78972</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2243,21 +2243,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2267,10 +2267,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>583125</v>
+        <v>582870</v>
       </c>
       <c r="R18" t="n">
-        <v>7079741</v>
+        <v>7079809</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2620,10 +2620,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125412823</v>
+        <v>125412758</v>
       </c>
       <c r="B22" t="n">
-        <v>78972</v>
+        <v>80075</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2631,21 +2631,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2655,10 +2655,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>582969</v>
+        <v>582922</v>
       </c>
       <c r="R22" t="n">
-        <v>7079681</v>
+        <v>7079716</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2717,10 +2717,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125412758</v>
+        <v>125412823</v>
       </c>
       <c r="B23" t="n">
-        <v>80075</v>
+        <v>78972</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2728,21 +2728,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2752,10 +2752,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>582922</v>
+        <v>582969</v>
       </c>
       <c r="R23" t="n">
-        <v>7079716</v>
+        <v>7079681</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -3008,32 +3008,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125409828</v>
+        <v>125410256</v>
       </c>
       <c r="B26" t="n">
-        <v>80075</v>
+        <v>92522</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3043,10 +3043,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>583020</v>
+        <v>583089</v>
       </c>
       <c r="R26" t="n">
-        <v>7079742</v>
+        <v>7079781</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3105,32 +3105,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125410256</v>
+        <v>125409828</v>
       </c>
       <c r="B27" t="n">
-        <v>92522</v>
+        <v>80075</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3140,10 +3140,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>583089</v>
+        <v>583020</v>
       </c>
       <c r="R27" t="n">
-        <v>7079781</v>
+        <v>7079742</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3202,32 +3202,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125409301</v>
+        <v>125409344</v>
       </c>
       <c r="B28" t="n">
-        <v>80103</v>
+        <v>75067</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6461</v>
+        <v>6440</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3299,32 +3299,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125409344</v>
+        <v>125409301</v>
       </c>
       <c r="B29" t="n">
-        <v>75067</v>
+        <v>80103</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6440</v>
+        <v>6461</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>

--- a/artfynd/A 33964-2023 artfynd.xlsx
+++ b/artfynd/A 33964-2023 artfynd.xlsx
@@ -2911,10 +2911,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125410318</v>
+        <v>125409828</v>
       </c>
       <c r="B25" t="n">
-        <v>92714</v>
+        <v>80075</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2922,21 +2922,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2079</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2946,10 +2946,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>583090</v>
+        <v>583020</v>
       </c>
       <c r="R25" t="n">
-        <v>7079781</v>
+        <v>7079742</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3008,32 +3008,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125410256</v>
+        <v>125410318</v>
       </c>
       <c r="B26" t="n">
-        <v>92522</v>
+        <v>92714</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4364</v>
+        <v>2079</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3043,7 +3043,7 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>583089</v>
+        <v>583090</v>
       </c>
       <c r="R26" t="n">
         <v>7079781</v>
@@ -3105,32 +3105,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125409828</v>
+        <v>125410256</v>
       </c>
       <c r="B27" t="n">
-        <v>80075</v>
+        <v>92522</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3140,10 +3140,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>583020</v>
+        <v>583089</v>
       </c>
       <c r="R27" t="n">
-        <v>7079742</v>
+        <v>7079781</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>

--- a/artfynd/A 33964-2023 artfynd.xlsx
+++ b/artfynd/A 33964-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY30"/>
+  <dimension ref="A1:AY32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125409866</v>
+        <v>125410683</v>
       </c>
       <c r="B2" t="n">
-        <v>82784</v>
+        <v>78993</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1312</v>
+        <v>353</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>583043</v>
+        <v>583125</v>
       </c>
       <c r="R2" t="n">
-        <v>7079761</v>
+        <v>7079741</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -775,7 +775,7 @@
         <v>125408990</v>
       </c>
       <c r="B3" t="n">
-        <v>91232</v>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125412570</v>
+        <v>125409866</v>
       </c>
       <c r="B4" t="n">
-        <v>57648</v>
+        <v>83173</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,39 +880,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>1312</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Omsjöflärken, Omsjöflärken, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>582867</v>
+        <v>583043</v>
       </c>
       <c r="R4" t="n">
-        <v>7079848</v>
+        <v>7079761</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -971,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125411016</v>
+        <v>125410318</v>
       </c>
       <c r="B5" t="n">
-        <v>78730</v>
+        <v>91962</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -982,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6446</v>
+        <v>2079</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1006,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>583096</v>
+        <v>583090</v>
       </c>
       <c r="R5" t="n">
-        <v>7079716</v>
+        <v>7079781</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1068,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125412381</v>
+        <v>125410122</v>
       </c>
       <c r="B6" t="n">
-        <v>80075</v>
+        <v>93197</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1079,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1103,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>582862</v>
+        <v>583046</v>
       </c>
       <c r="R6" t="n">
-        <v>7079873</v>
+        <v>7079760</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1165,10 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125408929</v>
+        <v>125410256</v>
       </c>
       <c r="B7" t="n">
-        <v>91250</v>
+        <v>93197</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1176,21 +1171,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1200,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>582879</v>
+        <v>583089</v>
       </c>
       <c r="R7" t="n">
-        <v>7079836</v>
+        <v>7079781</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1262,14 +1257,14 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125412210</v>
+        <v>125408385</v>
       </c>
       <c r="B8" t="n">
-        <v>78972</v>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1297,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>582813</v>
+        <v>582906</v>
       </c>
       <c r="R8" t="n">
-        <v>7079908</v>
+        <v>7079758</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1359,32 +1354,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125410480</v>
+        <v>125408754</v>
       </c>
       <c r="B9" t="n">
-        <v>78731</v>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1394,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>583113</v>
+        <v>582870</v>
       </c>
       <c r="R9" t="n">
-        <v>7079748</v>
+        <v>7079809</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1456,14 +1451,14 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125409899</v>
+        <v>125409242</v>
       </c>
       <c r="B10" t="n">
-        <v>78972</v>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -1491,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>583044</v>
+        <v>582988</v>
       </c>
       <c r="R10" t="n">
-        <v>7079761</v>
+        <v>7079828</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1553,32 +1548,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125410433</v>
+        <v>125409899</v>
       </c>
       <c r="B11" t="n">
-        <v>80075</v>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1588,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>583110</v>
+        <v>583044</v>
       </c>
       <c r="R11" t="n">
-        <v>7079768</v>
+        <v>7079761</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1650,14 +1645,14 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125409242</v>
+        <v>125412210</v>
       </c>
       <c r="B12" t="n">
-        <v>78972</v>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -1685,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>582988</v>
+        <v>582813</v>
       </c>
       <c r="R12" t="n">
-        <v>7079828</v>
+        <v>7079908</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1747,14 +1742,14 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125412777</v>
+        <v>125412472</v>
       </c>
       <c r="B13" t="n">
-        <v>78972</v>
+        <v>79327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -1782,10 +1777,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>582936</v>
+        <v>582841</v>
       </c>
       <c r="R13" t="n">
-        <v>7079714</v>
+        <v>7079874</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1844,32 +1839,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125410122</v>
+        <v>125412777</v>
       </c>
       <c r="B14" t="n">
-        <v>92522</v>
+        <v>79327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1879,10 +1874,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>583046</v>
+        <v>582936</v>
       </c>
       <c r="R14" t="n">
-        <v>7079760</v>
+        <v>7079714</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -1941,14 +1936,14 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125408385</v>
+        <v>125412823</v>
       </c>
       <c r="B15" t="n">
-        <v>78972</v>
+        <v>79327</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -1976,10 +1971,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>582906</v>
+        <v>582969</v>
       </c>
       <c r="R15" t="n">
-        <v>7079758</v>
+        <v>7079681</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2038,32 +2033,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125412324</v>
+        <v>125412906</v>
       </c>
       <c r="B16" t="n">
-        <v>80103</v>
+        <v>79327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2073,10 +2068,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>582860</v>
+        <v>582971</v>
       </c>
       <c r="R16" t="n">
-        <v>7079878</v>
+        <v>7079630</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2135,10 +2130,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125410683</v>
+        <v>125409344</v>
       </c>
       <c r="B17" t="n">
-        <v>78639</v>
+        <v>83307</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2146,21 +2141,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>353</v>
+        <v>6440</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2170,10 +2165,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>583125</v>
+        <v>582972</v>
       </c>
       <c r="R17" t="n">
-        <v>7079741</v>
+        <v>7079774</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2232,10 +2227,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125408754</v>
+        <v>125411016</v>
       </c>
       <c r="B18" t="n">
-        <v>78972</v>
+        <v>79084</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2243,21 +2238,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2267,10 +2262,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>582870</v>
+        <v>583096</v>
       </c>
       <c r="R18" t="n">
-        <v>7079809</v>
+        <v>7079716</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2329,10 +2324,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125412291</v>
+        <v>125409828</v>
       </c>
       <c r="B19" t="n">
-        <v>80075</v>
+        <v>80432</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2364,10 +2359,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>582860</v>
+        <v>583020</v>
       </c>
       <c r="R19" t="n">
-        <v>7079878</v>
+        <v>7079742</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2426,10 +2421,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125412906</v>
+        <v>125410376</v>
       </c>
       <c r="B20" t="n">
-        <v>78972</v>
+        <v>80432</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2437,21 +2432,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2461,10 +2456,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>582971</v>
+        <v>583092</v>
       </c>
       <c r="R20" t="n">
-        <v>7079630</v>
+        <v>7079777</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2523,10 +2518,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125410376</v>
+        <v>125410433</v>
       </c>
       <c r="B21" t="n">
-        <v>80075</v>
+        <v>80432</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2558,10 +2553,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>583092</v>
+        <v>583110</v>
       </c>
       <c r="R21" t="n">
-        <v>7079777</v>
+        <v>7079768</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2620,10 +2615,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125412758</v>
+        <v>125411154</v>
       </c>
       <c r="B22" t="n">
-        <v>80075</v>
+        <v>80432</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2655,10 +2650,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>582922</v>
+        <v>583150</v>
       </c>
       <c r="R22" t="n">
-        <v>7079716</v>
+        <v>7079809</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2717,10 +2712,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125412823</v>
+        <v>125412291</v>
       </c>
       <c r="B23" t="n">
-        <v>78972</v>
+        <v>80432</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2728,21 +2723,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2752,10 +2747,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>582969</v>
+        <v>582860</v>
       </c>
       <c r="R23" t="n">
-        <v>7079681</v>
+        <v>7079878</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -2814,32 +2809,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125412399</v>
+        <v>125412381</v>
       </c>
       <c r="B24" t="n">
-        <v>80104</v>
+        <v>80432</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2849,10 +2844,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>582861</v>
+        <v>582862</v>
       </c>
       <c r="R24" t="n">
-        <v>7079872</v>
+        <v>7079873</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -2911,10 +2906,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125409828</v>
+        <v>125412758</v>
       </c>
       <c r="B25" t="n">
-        <v>80075</v>
+        <v>80432</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2946,10 +2941,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>583020</v>
+        <v>582922</v>
       </c>
       <c r="R25" t="n">
-        <v>7079742</v>
+        <v>7079716</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3008,32 +3003,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125410318</v>
+        <v>125409301</v>
       </c>
       <c r="B26" t="n">
-        <v>92714</v>
+        <v>80460</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2079</v>
+        <v>6461</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3043,10 +3038,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>583090</v>
+        <v>582972</v>
       </c>
       <c r="R26" t="n">
-        <v>7079781</v>
+        <v>7079774</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3105,10 +3100,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125410256</v>
+        <v>125412324</v>
       </c>
       <c r="B27" t="n">
-        <v>92522</v>
+        <v>80460</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3116,21 +3111,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4364</v>
+        <v>6461</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3140,10 +3135,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>583089</v>
+        <v>582860</v>
       </c>
       <c r="R27" t="n">
-        <v>7079781</v>
+        <v>7079878</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3202,32 +3197,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125409344</v>
+        <v>125412399</v>
       </c>
       <c r="B28" t="n">
-        <v>75067</v>
+        <v>80461</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6440</v>
+        <v>6462</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3237,10 +3232,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>582972</v>
+        <v>582861</v>
       </c>
       <c r="R28" t="n">
-        <v>7079774</v>
+        <v>7079872</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3299,10 +3294,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125409301</v>
+        <v>125412570</v>
       </c>
       <c r="B29" t="n">
-        <v>80103</v>
+        <v>57950</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3310,34 +3305,39 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6461</v>
+        <v>100049</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Omsjöflärken, Omsjöflärken, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>582972</v>
+        <v>582867</v>
       </c>
       <c r="R29" t="n">
-        <v>7079774</v>
+        <v>7079848</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3396,10 +3396,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125412472</v>
+        <v>125412100</v>
       </c>
       <c r="B30" t="n">
-        <v>78972</v>
+        <v>57953</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3407,34 +3407,39 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Omsjöflärken, Omsjöflärken, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>582841</v>
+        <v>582812</v>
       </c>
       <c r="R30" t="n">
-        <v>7079874</v>
+        <v>7079992</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3469,6 +3474,11 @@
           <t>2025-05-25</t>
         </is>
       </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Äldre ringhack, tall</t>
+        </is>
+      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
@@ -3490,6 +3500,200 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>125410480</v>
+      </c>
+      <c r="B31" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Omsjöflärken, Omsjöflärken, Ång</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>583113</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7079748</v>
+      </c>
+      <c r="S31" t="n">
+        <v>15</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>125410902</v>
+      </c>
+      <c r="B32" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Omsjöflärken, Omsjöflärken, Ång</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>583119</v>
+      </c>
+      <c r="R32" t="n">
+        <v>7079757</v>
+      </c>
+      <c r="S32" t="n">
+        <v>15</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 33964-2023 artfynd.xlsx
+++ b/artfynd/A 33964-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY32"/>
+  <dimension ref="A1:AZ32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125410683</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125408990</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125409866</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125410318</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125410122</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125410256</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125408385</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1448,6 +1488,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125408754</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1545,6 +1590,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125409242</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1642,6 +1692,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125409899</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1739,6 +1794,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125412210</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1836,6 +1896,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125412472</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1933,6 +1998,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125412777</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2030,6 +2100,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125412823</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2127,6 +2202,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125412906</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2224,6 +2304,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125409344</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2321,6 +2406,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125411016</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2418,6 +2508,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125409828</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2515,6 +2610,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125410376</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2612,6 +2712,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125410433</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2709,6 +2814,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125411154</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2806,6 +2916,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125412291</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2903,6 +3018,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125412381</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3000,6 +3120,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125412758</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3097,6 +3222,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125409301</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3194,6 +3324,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125412324</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3291,6 +3426,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125412399</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3393,6 +3533,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125412570</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3500,6 +3645,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125412100</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3597,6 +3747,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125410480</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3694,8 +3849,46 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125410902</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>